--- a/Outputs/Scenarios/PtX_demand_ES_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_ES_Electrification.xlsx
@@ -513,7 +513,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02095094329260161</v>
+        <v>0.0209509432926016</v>
       </c>
       <c r="J2" t="n">
         <v>0.0016628469142822</v>
@@ -550,7 +550,7 @@
         <v>2.368540098542128e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001285496094224801</v>
+        <v>0.0012854960942248</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>2.557953848736361e-19</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05441508687977328</v>
+        <v>0.05441508687977327</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -908,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.006807962910043614</v>
+        <v>0.006807962910043613</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1534,7 +1534,7 @@
         <v>0.03004867080792004</v>
       </c>
       <c r="D30" t="n">
-        <v>0.00959732877350267</v>
+        <v>0.009597328773502672</v>
       </c>
       <c r="E30" t="n">
         <v>0.02766812693793468</v>
@@ -1555,7 +1555,7 @@
         <v>0.002669514355199396</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0967106542174956</v>
+        <v>0.09671065421749558</v>
       </c>
     </row>
     <row r="31">
@@ -1571,7 +1571,7 @@
         <v>0.02014781746142522</v>
       </c>
       <c r="D31" t="n">
-        <v>0.003077719302062993</v>
+        <v>0.003077719302062994</v>
       </c>
       <c r="E31" t="n">
         <v>0.01257642133542485</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0967106542174956</v>
+        <v>0.09671065421749558</v>
       </c>
     </row>
     <row r="34">

--- a/Outputs/Scenarios/PtX_demand_ES_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_ES_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.001803265043043054</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01644795514168909</v>
+        <v>0.01785131107648858</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.002741325856948182</v>
+        <v>0.00359750304517197</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01096530342779273</v>
+        <v>0.01439001218068788</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01644795514168909</v>
+        <v>0.01439001218068788</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0.0001445139968417573</v>
       </c>
       <c r="K24" t="n">
-        <v>0.02291013686100342</v>
+        <v>0.02249219748926903</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.0008747435269146214</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2228052657653926</v>
+        <v>0.2187407290339859</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>2.598199685446796e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.002741325856948182</v>
+        <v>0.00359750304517197</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.002669514355199396</v>
       </c>
       <c r="K30" t="n">
-        <v>0.09671065421749558</v>
+        <v>0.09622121384243575</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0161184423695826</v>
+        <v>0.01939107488100511</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0644737694783304</v>
+        <v>0.07756429952402043</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.09671065421749558</v>
+        <v>0.07756429952402043</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0001405007555368104</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0161184423695826</v>
+        <v>0.01939107488100511</v>
       </c>
     </row>
     <row r="43">
